--- a/src/test/java/org/olat/modules/curriculum/ui/importwizard/products-finish-test.xlsx
+++ b/src/test/java/org/olat/modules/curriculum/ui/importwizard/products-finish-test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/srosse/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C0777D-06CE-4C45-B15B-6001494E1713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1170CB6-284F-FE45-93D0-C6BC47ED39EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="7240" windowWidth="44600" windowHeight="19180" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="7240" windowWidth="44600" windowHeight="19180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
     <sheet name="Export Information" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Implementations!$A$1:$U$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Implementations!$A$1:$V$5</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
   <si>
     <t>Title *</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>Expiration date</t>
+  </si>
+  <si>
+    <t>Rooms</t>
   </si>
 </sst>
 </file>
@@ -696,7 +699,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -713,16 +716,17 @@
     <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.1640625" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -765,29 +769,32 @@
       <c r="N1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>61</v>
       </c>
@@ -815,26 +822,26 @@
       <c r="J2" s="5">
         <v>46129</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="P2" t="s">
-        <v>30</v>
       </c>
       <c r="Q2" t="s">
         <v>30</v>
       </c>
       <c r="R2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
         <v>31</v>
       </c>
-      <c r="T2" s="11">
+      <c r="U2" s="11">
         <v>46034.63958333333</v>
       </c>
-      <c r="U2" s="11">
+      <c r="V2" s="11">
         <v>46036.63958333333</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>61</v>
       </c>
@@ -862,26 +869,26 @@
       <c r="J3" s="5">
         <v>46125</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="P3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>8</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>31</v>
       </c>
-      <c r="T3" s="11">
+      <c r="U3" s="11">
         <v>46034.63958333333</v>
       </c>
-      <c r="U3" s="11">
+      <c r="V3" s="11">
         <v>46036.63958333333</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
@@ -909,26 +916,26 @@
       <c r="J4" s="5">
         <v>46125</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="P4" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>31</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>8</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>31</v>
       </c>
-      <c r="T4" s="11">
+      <c r="U4" s="11">
         <v>46034.63958333333</v>
       </c>
-      <c r="U4" s="11">
+      <c r="V4" s="11">
         <v>46036.63958333333</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -956,324 +963,324 @@
       <c r="J5" s="5">
         <v>46125</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="P5" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>31</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>8</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>31</v>
       </c>
-      <c r="T5" s="11">
+      <c r="U5" s="11">
         <v>46034.63958333333</v>
       </c>
-      <c r="U5" s="11">
+      <c r="V5" s="11">
         <v>46036.63958333333</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E8"/>
       <c r="F8"/>
       <c r="H8"/>
       <c r="I8"/>
       <c r="K8"/>
-      <c r="O8"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P8"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E9"/>
       <c r="F9"/>
       <c r="H9"/>
       <c r="I9"/>
       <c r="K9"/>
-      <c r="O9"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P9"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E10"/>
       <c r="F10"/>
       <c r="H10"/>
       <c r="I10"/>
       <c r="K10"/>
-      <c r="O10"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P10"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E11"/>
       <c r="F11"/>
       <c r="H11"/>
       <c r="I11"/>
       <c r="K11"/>
-      <c r="O11"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P11"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E12"/>
       <c r="F12"/>
       <c r="H12"/>
       <c r="I12"/>
       <c r="K12"/>
-      <c r="O12"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P12"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E13"/>
       <c r="F13"/>
       <c r="H13"/>
       <c r="I13"/>
       <c r="K13"/>
-      <c r="O13"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P13"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E14"/>
       <c r="F14"/>
       <c r="H14"/>
       <c r="I14"/>
       <c r="K14"/>
-      <c r="O14"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P14"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E15"/>
       <c r="F15"/>
       <c r="H15"/>
       <c r="I15"/>
       <c r="K15"/>
-      <c r="O15"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P15"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E16"/>
       <c r="F16"/>
       <c r="H16"/>
       <c r="I16"/>
       <c r="K16"/>
-      <c r="O16"/>
-    </row>
-    <row r="17" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P16"/>
+    </row>
+    <row r="17" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E17"/>
       <c r="F17"/>
       <c r="H17"/>
       <c r="I17"/>
       <c r="K17"/>
-      <c r="O17"/>
-    </row>
-    <row r="18" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P17"/>
+    </row>
+    <row r="18" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E18"/>
       <c r="F18"/>
       <c r="H18"/>
       <c r="I18"/>
       <c r="K18"/>
-      <c r="O18"/>
-    </row>
-    <row r="19" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P18"/>
+    </row>
+    <row r="19" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E19"/>
       <c r="F19"/>
       <c r="H19"/>
       <c r="I19"/>
       <c r="K19"/>
-      <c r="O19"/>
-    </row>
-    <row r="20" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P19"/>
+    </row>
+    <row r="20" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E20"/>
       <c r="F20"/>
       <c r="H20"/>
       <c r="I20"/>
       <c r="K20"/>
-      <c r="O20"/>
-    </row>
-    <row r="21" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P20"/>
+    </row>
+    <row r="21" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E21"/>
       <c r="F21"/>
       <c r="H21"/>
       <c r="I21"/>
       <c r="K21"/>
-      <c r="O21"/>
-    </row>
-    <row r="22" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P21"/>
+    </row>
+    <row r="22" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E22"/>
       <c r="F22"/>
       <c r="H22"/>
       <c r="I22"/>
       <c r="K22"/>
-      <c r="O22"/>
-    </row>
-    <row r="23" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P22"/>
+    </row>
+    <row r="23" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E23"/>
       <c r="F23"/>
       <c r="H23"/>
       <c r="I23"/>
       <c r="K23"/>
-      <c r="O23"/>
-    </row>
-    <row r="24" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P23"/>
+    </row>
+    <row r="24" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E24"/>
       <c r="F24"/>
       <c r="H24"/>
       <c r="I24"/>
       <c r="K24"/>
-      <c r="O24"/>
-    </row>
-    <row r="25" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P24"/>
+    </row>
+    <row r="25" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E25"/>
       <c r="F25"/>
       <c r="H25"/>
       <c r="I25"/>
       <c r="K25"/>
-      <c r="O25"/>
-    </row>
-    <row r="26" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P25"/>
+    </row>
+    <row r="26" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E26"/>
       <c r="F26"/>
       <c r="H26"/>
       <c r="I26"/>
       <c r="K26"/>
-      <c r="O26"/>
-    </row>
-    <row r="27" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P26"/>
+    </row>
+    <row r="27" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E27"/>
       <c r="F27"/>
       <c r="H27"/>
       <c r="I27"/>
       <c r="K27"/>
-      <c r="O27"/>
-    </row>
-    <row r="28" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P27"/>
+    </row>
+    <row r="28" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E28"/>
       <c r="F28"/>
       <c r="H28"/>
       <c r="I28"/>
       <c r="K28"/>
-      <c r="O28"/>
-    </row>
-    <row r="29" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P28"/>
+    </row>
+    <row r="29" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E29"/>
       <c r="F29"/>
       <c r="H29"/>
       <c r="I29"/>
       <c r="K29"/>
-      <c r="O29"/>
-    </row>
-    <row r="30" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P29"/>
+    </row>
+    <row r="30" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E30"/>
       <c r="F30"/>
       <c r="H30"/>
       <c r="I30"/>
       <c r="K30"/>
-      <c r="O30"/>
-    </row>
-    <row r="31" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P30"/>
+    </row>
+    <row r="31" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E31"/>
       <c r="F31"/>
       <c r="H31"/>
       <c r="I31"/>
       <c r="K31"/>
-      <c r="O31"/>
-    </row>
-    <row r="32" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P31"/>
+    </row>
+    <row r="32" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E32"/>
       <c r="F32"/>
       <c r="H32"/>
       <c r="I32"/>
       <c r="K32"/>
-      <c r="O32"/>
-    </row>
-    <row r="33" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P32"/>
+    </row>
+    <row r="33" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E33"/>
       <c r="F33"/>
       <c r="H33"/>
       <c r="I33"/>
       <c r="K33"/>
-      <c r="O33"/>
-    </row>
-    <row r="34" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P33"/>
+    </row>
+    <row r="34" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E34"/>
       <c r="F34"/>
       <c r="H34"/>
       <c r="I34"/>
       <c r="K34"/>
-      <c r="O34"/>
-    </row>
-    <row r="35" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P34"/>
+    </row>
+    <row r="35" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E35"/>
       <c r="F35"/>
       <c r="H35"/>
       <c r="I35"/>
       <c r="K35"/>
-      <c r="O35"/>
-    </row>
-    <row r="36" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P35"/>
+    </row>
+    <row r="36" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E36"/>
       <c r="F36"/>
       <c r="H36"/>
       <c r="I36"/>
       <c r="K36"/>
-      <c r="O36"/>
-    </row>
-    <row r="37" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P36"/>
+    </row>
+    <row r="37" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E37"/>
       <c r="F37"/>
       <c r="H37"/>
       <c r="I37"/>
       <c r="K37"/>
-      <c r="O37"/>
-    </row>
-    <row r="38" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P37"/>
+    </row>
+    <row r="38" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E38"/>
       <c r="F38"/>
       <c r="H38"/>
       <c r="I38"/>
       <c r="K38"/>
-      <c r="O38"/>
-    </row>
-    <row r="39" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P38"/>
+    </row>
+    <row r="39" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E39"/>
       <c r="F39"/>
       <c r="H39"/>
       <c r="I39"/>
       <c r="K39"/>
-      <c r="O39"/>
-    </row>
-    <row r="40" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P39"/>
+    </row>
+    <row r="40" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E40"/>
       <c r="F40"/>
       <c r="H40"/>
       <c r="I40"/>
       <c r="K40"/>
-      <c r="O40"/>
-    </row>
-    <row r="41" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P40"/>
+    </row>
+    <row r="41" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E41"/>
       <c r="F41"/>
       <c r="H41"/>
       <c r="I41"/>
       <c r="K41"/>
-      <c r="O41"/>
-    </row>
-    <row r="42" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P41"/>
+    </row>
+    <row r="42" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E42"/>
       <c r="F42"/>
       <c r="H42"/>
       <c r="I42"/>
       <c r="K42"/>
-      <c r="O42"/>
-    </row>
-    <row r="43" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P42"/>
+    </row>
+    <row r="43" spans="5:16" x14ac:dyDescent="0.2">
       <c r="E43"/>
       <c r="F43"/>
       <c r="H43"/>
       <c r="I43"/>
       <c r="K43"/>
-      <c r="O43"/>
-    </row>
-    <row r="44" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="P43"/>
+    </row>
+    <row r="44" spans="5:16" x14ac:dyDescent="0.2">
       <c r="F44"/>
       <c r="H44"/>
       <c r="I44"/>
       <c r="K44"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:V5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157500000008" bottom="0.78740157500000008" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
